--- a/approaches/examples/olive-oil/2B_market.xlsx
+++ b/approaches/examples/olive-oil/2B_market.xlsx
@@ -10,9 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Application (bottom-up)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Product Grade" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Extraction Method" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Distribution Channel" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Packaging Format" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Distribution Channel" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Packaging Format" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By SourceOrigin" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Evidence" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9256.9769</v>
+        <v>23655.3358</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1</v>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.1595364248991482</v>
+        <v>0.1454428729775208</v>
       </c>
     </row>
     <row r="8">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.1595364248991482</v>
+        <v>0.1454428729775208</v>
       </c>
     </row>
     <row r="9">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.01563820473614879</v>
+        <v>0.03791744947454942</v>
       </c>
     </row>
     <row r="10">
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.01563820473614879</v>
+        <v>0.03791744947454942</v>
       </c>
     </row>
     <row r="11">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>6781.6138</v>
+        <v>10937.2076</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.732594871226264</v>
+        <v>0.4623568945489245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Spain</t>
+          <t xml:space="preserve">   Italy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1906.57</v>
+        <v>3632.1939</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.2059603281498952</v>
+        <v>0.1535464949941653</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Italy</t>
+          <t xml:space="preserve">   Spain</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3212.7225</v>
+        <v>3398.7139</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.3470595783813612</v>
+        <v>0.1436764173941678</v>
       </c>
     </row>
     <row r="14">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>96.6688</v>
+        <v>619.2403</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.01044280449700593</v>
+        <v>0.02617761613005722</v>
       </c>
     </row>
     <row r="15">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>542.47</v>
+        <v>742.6</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.05860120489227968</v>
+        <v>0.03139249454239411</v>
       </c>
     </row>
     <row r="16">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>520.78</v>
+        <v>1328.5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.05625810733091491</v>
+        <v>0.05616069081547344</v>
       </c>
     </row>
     <row r="17">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>468.275</v>
+        <v>753.3029</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.05058616922766654</v>
+        <v>0.03184494637357885</v>
       </c>
     </row>
     <row r="18">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>34.1275</v>
+        <v>462.6566</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.00368667874714044</v>
+        <v>0.01955823429908782</v>
       </c>
     </row>
     <row r="19">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>185.125</v>
+        <v>1211.6</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>0.01999842950888211</v>
+        <v>0.05121888821379571</v>
       </c>
     </row>
     <row r="20">
@@ -785,52 +785,52 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>185.125</v>
+        <v>627.3</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.01999842950888211</v>
+        <v>0.02651832995750582</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Australia</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>584.3</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0.0247005582562899</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Middle East &amp; Africa</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>640.3876</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>0.06917891304233459</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tunisia</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>245.9463</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>0.02656874945858404</v>
+      <c r="C22" s="7" t="n">
+        <v>1407.5782</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>0.05950362370252212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Morocco</t>
+          <t xml:space="preserve">   Tunisia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>136.7425</v>
+        <v>278.7782</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.01477183117957224</v>
+        <v>0.01178500285757939</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Algeria</t>
+          <t xml:space="preserve">   Morocco</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>257.6988</v>
+        <v>1128.8</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.0278383324041783</v>
+        <v>0.04771862084494272</v>
       </c>
     </row>
     <row r="25">
@@ -875,16 +875,16 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>0.003053156587222336</v>
+        <v>0.2435602710826874</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Syria</t>
+          <t xml:space="preserve">   Rest of World</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.003053156587222336</v>
+        <v>0.2435602710826874</v>
       </c>
     </row>
   </sheetData>
@@ -944,27 +944,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Home Cooking and Table Use</t>
+          <t>Household culinary use</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Foodservice and Restaurant Operations</t>
+          <t>Foodservice and hospitality</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Processed Food Manufacturing</t>
+          <t>Food processing and manufacturing</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Infused and Flavored Olive Oil Production</t>
+          <t>Personal care and cosmetic formulations</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nutraceutical and Pharmaceutical Applications</t>
+          <t>Nutraceutical and pharmaceutical use</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>342.5469</v>
+        <v>17245.3261</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5947.5</v>
+        <v>4892.8494</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2604</v>
+        <v>155.3946</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>306.15</v>
+        <v>708.3727</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>56.78</v>
+        <v>653.393</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>9256.9769</v>
+        <v>23655.3358</v>
       </c>
     </row>
     <row r="5">
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>143.325</v>
+        <v>2550</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>780</v>
+        <v>600</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>504</v>
+        <v>28</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>32.5</v>
+        <v>135</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>17</v>
+        <v>127.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
     </row>
     <row r="6">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>143.325</v>
+        <v>2550</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>780</v>
+        <v>600</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>504</v>
+        <v>28</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>32.5</v>
+        <v>135</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>17</v>
+        <v>127.5</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
     </row>
     <row r="7">
@@ -1055,22 +1055,22 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>30.7125</v>
+        <v>850</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>105</v>
+        <v>7.2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6.5</v>
+        <v>27</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2.55</v>
+        <v>12.75</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
     </row>
     <row r="8">
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>30.7125</v>
+        <v>850</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>105</v>
+        <v>7.2</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>6.5</v>
+        <v>27</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2.55</v>
+        <v>12.75</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
     </row>
     <row r="9">
@@ -1105,72 +1105,72 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>111.5888</v>
+        <v>7881.962</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4647.5</v>
+        <v>2178.3338</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1764</v>
+        <v>79.95910000000001</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>227.5</v>
+        <v>366.0189</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>31.025</v>
+        <v>430.9338</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>6781.6138</v>
+        <v>10937.2076</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Spain</t>
+          <t xml:space="preserve">   Italy</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>24.57</v>
+        <v>2540.6228</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1300</v>
+        <v>836.9109999999999</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>504</v>
+        <v>21.5206</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>78</v>
+        <v>80.7021</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0</v>
+        <v>152.4374</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1906.57</v>
+        <v>3632.1939</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Italy</t>
+          <t xml:space="preserve">   Spain</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>22.5225</v>
+        <v>2607.552</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2275</v>
+        <v>490.8333</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>840</v>
+        <v>19.6333</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>65</v>
+        <v>124.2422</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>10.2</v>
+        <v>156.4531</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>3212.7225</v>
+        <v>3398.7139</v>
       </c>
     </row>
     <row r="12">
@@ -1180,22 +1180,22 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>5.1188</v>
+        <v>430.8258</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0</v>
+        <v>119.2796</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>63</v>
+        <v>3.2439</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>26</v>
+        <v>22.8084</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2.55</v>
+        <v>43.0826</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>96.6688</v>
+        <v>619.2403</v>
       </c>
     </row>
     <row r="13">
@@ -1205,22 +1205,22 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4.095</v>
+        <v>510</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>520</v>
+        <v>180</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>16.25</v>
+        <v>36</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2.125</v>
+        <v>10.2</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>542.47</v>
+        <v>742.6</v>
       </c>
     </row>
     <row r="14">
@@ -1230,22 +1230,22 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>16.38</v>
+        <v>1020</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>292.5</v>
+        <v>200</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>19.5</v>
+        <v>54</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.4</v>
+        <v>42.5</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>520.78</v>
+        <v>1328.5</v>
       </c>
     </row>
     <row r="15">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>20.475</v>
+        <v>495.4981</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>260</v>
+        <v>209.858</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>168</v>
+        <v>9.327</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>13</v>
+        <v>26.2323</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>6.8</v>
+        <v>12.3875</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>468.275</v>
+        <v>753.3029</v>
       </c>
     </row>
     <row r="16">
@@ -1280,22 +1280,22 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>18.4275</v>
+        <v>277.4633</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0</v>
+        <v>141.4519</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0</v>
+        <v>7.8343</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>9.75</v>
+        <v>22.0339</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>5.95</v>
+        <v>13.8732</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>34.1275</v>
+        <v>462.6566</v>
       </c>
     </row>
     <row r="17">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>40.95</v>
+        <v>935</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>84</v>
+        <v>11.2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5.2</v>
+        <v>45</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2.975</v>
+        <v>20.4</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>185.125</v>
+        <v>1211.6</v>
       </c>
     </row>
     <row r="18">
@@ -1330,122 +1330,122 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>40.95</v>
+        <v>552.5</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>5.2</v>
+        <v>31.5</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2.975</v>
+        <v>15.3</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>185.125</v>
+        <v>627.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Australia</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>584.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Middle East &amp; Africa</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>14.3326</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>468</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>126</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>2.805</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>640.3876</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tunisia</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>3.0713</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>195</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>1.275</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>245.9463</v>
+      <c r="B20" s="7" t="n">
+        <v>1203.3641</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>114.5156</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>5.0355</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>22.8538</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>61.8092</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>1407.5782</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Morocco</t>
+          <t xml:space="preserve">   Tunisia</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>6.1425</v>
+        <v>183.3641</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>78</v>
+        <v>34.5156</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>42</v>
+        <v>1.0355</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9.75</v>
+        <v>4.8538</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.85</v>
+        <v>55.0092</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>136.7425</v>
+        <v>278.7782</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Algeria</t>
+          <t xml:space="preserve">   Morocco</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>5.1188</v>
+        <v>1020</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>50.4</v>
+        <v>4</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>6.5</v>
+        <v>18</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.68</v>
+        <v>6.8</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>257.6988</v>
+        <v>1128.8</v>
       </c>
     </row>
     <row r="23">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1.638</v>
+        <v>3825</v>
       </c>
       <c r="C23" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="F23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0.425</v>
-      </c>
       <c r="G23" s="7" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Syria</t>
+          <t xml:space="preserve">   Rest of World</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>1.638</v>
+        <v>3825</v>
       </c>
       <c r="C24" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="F24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>0.425</v>
-      </c>
       <c r="G24" s="9" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
     </row>
   </sheetData>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Refined Olive Oil (including blends with virgin)</t>
+          <t>Refined Olive Oil</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Olive-Pomace Oil</t>
+          <t>Blended/Refined Olive Oil (not elsewhere specified)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1573,19 +1573,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5037.3124</v>
+        <v>12709.43</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1433.2119</v>
+        <v>3822.5238</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2080.8735</v>
+        <v>4861.4543</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>705.5791</v>
+        <v>2261.9277</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9256.9769</v>
+        <v>23655.3358</v>
       </c>
     </row>
     <row r="5">
@@ -1595,19 +1595,19 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>959.9363</v>
+        <v>1892.275</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>147.6825</v>
+        <v>516.075</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>295.365</v>
+        <v>688.1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>73.8412</v>
+        <v>344.05</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
     </row>
     <row r="6">
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>959.9363</v>
+        <v>1892.275</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>147.6825</v>
+        <v>516.075</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>295.365</v>
+        <v>688.1</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>73.8412</v>
+        <v>344.05</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
     </row>
     <row r="7">
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>101.3337</v>
+        <v>448.475</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>11.581</v>
+        <v>134.5425</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26.0572</v>
+        <v>224.2375</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>5.7906</v>
+        <v>89.69499999999999</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
     </row>
     <row r="8">
@@ -1661,19 +1661,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>101.3337</v>
+        <v>448.475</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>11.581</v>
+        <v>134.5425</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>26.0572</v>
+        <v>224.2375</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>5.7906</v>
+        <v>89.69499999999999</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
     </row>
     <row r="9">
@@ -1683,63 +1683,63 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3529.3983</v>
+        <v>6346.5931</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>1134.0031</v>
+        <v>1858.3646</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1555.5239</v>
+        <v>1742.1351</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>562.6885</v>
+        <v>990.1147999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6781.6138</v>
+        <v>10937.2076</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Spain</t>
+          <t xml:space="preserve">   Italy</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>857.9565</v>
+        <v>2360.926</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>381.314</v>
+        <v>544.8291</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>476.6425</v>
+        <v>435.8633</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>190.657</v>
+        <v>290.5755</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1906.57</v>
+        <v>3632.1939</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Italy</t>
+          <t xml:space="preserve">   Spain</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1766.9974</v>
+        <v>1699.357</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>481.9084</v>
+        <v>679.7428</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>706.7989</v>
+        <v>679.7428</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>257.0178</v>
+        <v>339.8713</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>3212.7225</v>
+        <v>3398.7139</v>
       </c>
     </row>
     <row r="12">
@@ -1749,19 +1749,19 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>67.6682</v>
+        <v>464.4302</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>11.6003</v>
+        <v>74.30880000000001</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>12.5669</v>
+        <v>49.5392</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>4.8334</v>
+        <v>30.9621</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>96.6688</v>
+        <v>619.2403</v>
       </c>
     </row>
     <row r="13">
@@ -1771,19 +1771,19 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>298.3585</v>
+        <v>445.56</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>81.37050000000001</v>
+        <v>111.39</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>119.3434</v>
+        <v>111.39</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>43.3976</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>542.47</v>
+        <v>742.6</v>
       </c>
     </row>
     <row r="14">
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>260.39</v>
+        <v>730.675</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>104.156</v>
+        <v>265.7</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>114.5716</v>
+        <v>199.275</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>41.6624</v>
+        <v>132.85</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>520.78</v>
+        <v>1328.5</v>
       </c>
     </row>
     <row r="15">
@@ -1815,19 +1815,19 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>257.5512</v>
+        <v>414.3166</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>70.24120000000001</v>
+        <v>112.9954</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>117.0687</v>
+        <v>150.6606</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>23.4139</v>
+        <v>75.33029999999999</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>468.275</v>
+        <v>753.3029</v>
       </c>
     </row>
     <row r="16">
@@ -1837,19 +1837,19 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>20.4765</v>
+        <v>231.3283</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>3.4127</v>
+        <v>69.3985</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>8.5319</v>
+        <v>115.6642</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1.7064</v>
+        <v>46.2656</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>34.1275</v>
+        <v>462.6566</v>
       </c>
     </row>
     <row r="17">
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>120.3312</v>
+        <v>697.745</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>18.5125</v>
+        <v>181.74</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>37.025</v>
+        <v>210.955</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9.2563</v>
+        <v>121.16</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>185.125</v>
+        <v>1211.6</v>
       </c>
     </row>
     <row r="18">
@@ -1881,107 +1881,107 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>120.3312</v>
+        <v>376.38</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>18.5125</v>
+        <v>94.095</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>37.025</v>
+        <v>94.095</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9.2563</v>
+        <v>62.73</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>185.125</v>
+        <v>627.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Australia</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>321.365</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>87.645</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>116.86</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>584.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Middle East &amp; Africa</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>312.1814</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>115.7802</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>160.6845</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>51.7415</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>640.3876</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tunisia</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>147.5678</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>36.8919</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>49.1893</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>12.2973</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>245.9463</v>
+      <c r="B20" s="7" t="n">
+        <v>731.6669000000001</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>267.5767</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>267.5767</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>140.7579</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1407.5782</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Morocco</t>
+          <t xml:space="preserve">   Tunisia</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>61.5341</v>
+        <v>167.2669</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>27.3485</v>
+        <v>41.8167</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>34.1856</v>
+        <v>41.8167</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>13.6743</v>
+        <v>27.8779</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>136.7425</v>
+        <v>278.7782</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Algeria</t>
+          <t xml:space="preserve">   Morocco</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>103.0795</v>
+        <v>564.4</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>51.5398</v>
+        <v>225.76</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>77.3096</v>
+        <v>225.76</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>25.7699</v>
+        <v>112.88</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>257.6988</v>
+        <v>1128.8</v>
       </c>
     </row>
     <row r="23">
@@ -1991,41 +1991,41 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>14.1315</v>
+        <v>2592.675</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>5.6526</v>
+        <v>864.225</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>6.2179</v>
+        <v>1728.45</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2.261</v>
+        <v>576.15</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Syria</t>
+          <t xml:space="preserve">   Rest of World</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>14.1315</v>
+        <v>2592.675</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>5.6526</v>
+        <v>864.225</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>6.2179</v>
+        <v>1728.45</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2.261</v>
+        <v>576.15</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
     </row>
     <row r="26">
@@ -2053,51 +2053,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Refined Olive Oil (including blends with virgin)</t>
+          <t>Refined Olive Oil</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Olive-Pomace Oil</t>
+          <t>Blended/Refined Olive Oil (not elsewhere specified)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>0.12</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0.05</v>
@@ -2122,7 +2122,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
@@ -2132,16 +2132,16 @@
         <v>0.15</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
@@ -2151,10 +2151,10 @@
         <v>0.15</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="33">
@@ -2164,32 +2164,32 @@
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="C33" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0.1</v>
@@ -2198,7 +2198,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
@@ -2208,26 +2208,26 @@
         <v>0.2</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="C36" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D36" s="10" t="n">
         <v>0.2</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>0.3</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0.1</v>
@@ -2236,96 +2236,96 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="C37" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>0.1</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="C38" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D39" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Rest of World</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="C41" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>0.1</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -2334,1666 +2334,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>By Extraction Method -- TOP-DOWN (country total x share)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Evidence status: web_evidence_backed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Mechanical Extraction (Cold-Pressed / Cold-Extracted)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Mechanical Extraction (Hot-Pressed / Standard)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Chemical Extraction (Refining and Solvent Extraction)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>5959.2254</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2357.5117</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>940.2397999999999</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>9256.9769</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>1033.7775</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>265.8285</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>177.219</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>1476.825</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   United States</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>1033.7775</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>265.8285</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>177.219</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1476.825</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Latin America</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>86.8575</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>34.743</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>23.162</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>144.7625</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Brazil</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>86.8575</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>34.743</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>23.162</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>144.7625</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>4390.6404</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1770.6363</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>620.3371</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>6781.6138</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Spain</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>1182.0734</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>533.8396</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>190.657</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>1906.57</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Italy</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>2184.6513</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>771.0534</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>257.0178</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>3212.7225</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Greece</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>69.6015</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>21.2671</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>5.8002</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>96.6688</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Portugal</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>352.6055</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>146.4669</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>43.3976</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>542.47</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Turkey</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>270.8056</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>187.4808</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>62.4936</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>520.78</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   France</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>309.0615</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>103.0205</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>56.193</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>468.275</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Germany</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>21.8416</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>7.508</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>4.7779</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>34.1275</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>114.7775</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>40.7275</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>185.125</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Japan</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>114.7775</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>40.7275</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>185.125</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Middle East &amp; Africa</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>319.6063</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>234.8365</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>85.9448</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>640.3876</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tunisia</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>135.2705</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>81.1623</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>29.5135</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>245.9463</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Morocco</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>68.37130000000001</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>50.5947</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>17.7765</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>136.7425</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Algeria</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>115.9645</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>103.0795</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>38.6548</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>257.6988</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>13.5662</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>10.7399</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>3.9569</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>28.263</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Syria</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>13.5662</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>10.7399</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>3.9569</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>28.263</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Shares used (fraction of each country's total)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Mechanical Extraction (Cold-Pressed / Cold-Extracted)</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Mechanical Extraction (Hot-Pressed / Standard)</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Chemical Extraction (Refining and Solvent Extraction)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>By Distribution Channel -- TOP-DOWN (country total x share)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Evidence status: web_evidence_backed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Supermarkets and Hypermarkets</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Specialty Food Stores and Gourmet Retailers</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Online Retail</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Foodservice and Institutional</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Direct from Producer / Bulk Sales</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>4606.5234</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1132.7292</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>949.3779</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1608.7255</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>959.6209</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>9256.9769</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>812.2538</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>221.5238</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>206.7555</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>191.9873</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>44.3046</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>1476.825</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   United States</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>812.2538</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>221.5238</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>206.7555</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>191.9873</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>44.3046</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>1476.825</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Latin America</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>83.9622</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>14.4763</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>14.4763</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>23.162</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>8.685700000000001</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>144.7625</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Brazil</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>83.9622</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>14.4763</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>14.4763</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>23.162</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>8.685700000000001</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>144.7625</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>3354.4327</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>818.1267</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>666.6193</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>1260.4734</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>681.9617</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>6781.6138</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Spain</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>991.4164</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>190.657</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>190.657</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>381.314</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>152.5256</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>1906.57</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Italy</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>1542.1068</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>449.7812</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>321.2722</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>578.29</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>321.2723</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>3212.7225</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Greece</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>43.501</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>11.6003</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>7.7335</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>19.3338</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>14.5002</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>96.6688</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Portugal</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>271.235</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>54.247</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>48.8223</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>103.0693</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>65.0964</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>542.47</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Turkey</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>239.5588</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>46.8702</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>46.8702</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>93.74039999999999</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>93.74039999999999</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>520.78</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   France</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>248.1858</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>60.8757</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>46.8275</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>79.60680000000001</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>32.7792</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>468.275</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Germany</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>18.4289</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>4.0953</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>4.4366</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>5.1191</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>2.0476</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>34.1275</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>92.5625</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>25.9175</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>27.7688</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>9.2562</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>185.125</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Japan</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>92.5625</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>25.9175</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>27.7688</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>9.2562</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>185.125</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Middle East &amp; Africa</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>253.4202</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>47.2866</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>34.4788</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>101.0946</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>204.1074</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>640.3876</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tunisia</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>98.3785</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>19.6757</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>14.7568</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>39.3514</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>73.7839</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>245.9463</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Morocco</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>51.9622</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>9.571999999999999</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>6.8371</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>20.5114</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>47.8598</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>136.7425</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Algeria</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>103.0795</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>18.0389</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>12.8849</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>41.2318</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>82.4637</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>257.6988</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>9.891999999999999</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>1.6958</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>1.1305</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>4.2394</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>11.3053</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>28.263</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Syria</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>9.891999999999999</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>1.6958</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>1.1305</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>4.2394</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>11.3053</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>28.263</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Shares used (fraction of each country's total)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Supermarkets and Hypermarkets</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Specialty Food Stores and Gourmet Retailers</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Online Retail</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Foodservice and Institutional</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Direct from Producer / Bulk Sales</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4013,7 +2353,7 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>By Packaging Format -- TOP-DOWN (country total x share)</t>
+          <t>By Distribution Channel -- TOP-DOWN (country total x share)</t>
         </is>
       </c>
     </row>
@@ -4032,22 +2372,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Glass Bottles and Jars</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Plastic Bottles and Containers</t>
+          <t>Foodservice</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Metal Cans and Tins</t>
+          <t>Food Processing</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bulk (Drums, IBCs, Flexitanks)</t>
+          <t>Bulk/Industrial</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4063,19 +2403,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4179.3857</v>
+        <v>10347.0878</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1700.357</v>
+        <v>4337.4299</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1149.2532</v>
+        <v>5135.2535</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2227.981</v>
+        <v>3835.5646</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9256.9769</v>
+        <v>23655.3358</v>
       </c>
     </row>
     <row r="5">
@@ -4085,19 +2425,19 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>767.949</v>
+        <v>1892.275</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>324.9015</v>
+        <v>756.91</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>206.7555</v>
+        <v>619.29</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>177.219</v>
+        <v>172.025</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
     </row>
     <row r="6">
@@ -4107,19 +2447,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>767.949</v>
+        <v>1892.275</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>324.9015</v>
+        <v>756.91</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>206.7555</v>
+        <v>619.29</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>177.219</v>
+        <v>172.025</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>1476.825</v>
+        <v>3440.5</v>
       </c>
     </row>
     <row r="7">
@@ -4129,19 +2469,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>66.5907</v>
+        <v>430.536</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>34.743</v>
+        <v>179.39</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>21.7144</v>
+        <v>215.268</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>21.7144</v>
+        <v>71.756</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
     </row>
     <row r="8">
@@ -4151,19 +2491,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>66.5907</v>
+        <v>430.536</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>34.743</v>
+        <v>179.39</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>21.7144</v>
+        <v>215.268</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>21.7144</v>
+        <v>71.756</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>144.7625</v>
+        <v>896.95</v>
       </c>
     </row>
     <row r="9">
@@ -4173,63 +2513,63 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3052.9792</v>
+        <v>4417.4672</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>1171.2503</v>
+        <v>1915.3551</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>803.8386</v>
+        <v>2486.7539</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1753.5457</v>
+        <v>2117.6314</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6781.6138</v>
+        <v>10937.2076</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Spain</t>
+          <t xml:space="preserve">   Italy</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>800.7594</v>
+        <v>1525.5214</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>343.1826</v>
+        <v>653.7949</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>228.7884</v>
+        <v>799.0827</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>533.8396</v>
+        <v>653.7949</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1906.57</v>
+        <v>3632.1939</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Italy</t>
+          <t xml:space="preserve">   Spain</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1542.1068</v>
+        <v>1087.5884</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>514.0356</v>
+        <v>509.8071</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>353.3995</v>
+        <v>849.6785</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>803.1806</v>
+        <v>951.6399</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>3212.7225</v>
+        <v>3398.7139</v>
       </c>
     </row>
     <row r="12">
@@ -4239,19 +2579,19 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>43.501</v>
+        <v>297.2353</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>16.4337</v>
+        <v>136.2329</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>12.5669</v>
+        <v>111.4633</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>24.1672</v>
+        <v>74.30880000000001</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>96.6688</v>
+        <v>619.2403</v>
       </c>
     </row>
     <row r="13">
@@ -4261,19 +2601,19 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>238.6868</v>
+        <v>334.17</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>97.6446</v>
+        <v>133.668</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>70.5211</v>
+        <v>163.372</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>135.6175</v>
+        <v>111.39</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>542.47</v>
+        <v>742.6</v>
       </c>
     </row>
     <row r="14">
@@ -4283,19 +2623,19 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>177.0652</v>
+        <v>531.4</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>104.156</v>
+        <v>199.275</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>72.9092</v>
+        <v>332.125</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>166.6496</v>
+        <v>265.7</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>520.78</v>
+        <v>1328.5</v>
       </c>
     </row>
     <row r="15">
@@ -4305,19 +2645,19 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>234.1375</v>
+        <v>391.7175</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>88.9723</v>
+        <v>180.7927</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>60.8757</v>
+        <v>143.1276</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>84.2895</v>
+        <v>37.6651</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>468.275</v>
+        <v>753.3029</v>
       </c>
     </row>
     <row r="16">
@@ -4327,19 +2667,19 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>16.7225</v>
+        <v>249.8346</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>6.8255</v>
+        <v>101.7845</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>4.7778</v>
+        <v>87.90479999999999</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>5.8017</v>
+        <v>23.1327</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>34.1275</v>
+        <v>462.6566</v>
       </c>
     </row>
     <row r="17">
@@ -4349,19 +2689,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>94.41379999999999</v>
+        <v>605.8</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>38.8762</v>
+        <v>285.371</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>29.62</v>
+        <v>242.32</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22.215</v>
+        <v>78.10899999999999</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>185.125</v>
+        <v>1211.6</v>
       </c>
     </row>
     <row r="18">
@@ -4371,107 +2711,107 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>94.41379999999999</v>
+        <v>313.65</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>38.8762</v>
+        <v>156.825</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>29.62</v>
+        <v>125.46</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>22.215</v>
+        <v>31.365</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>185.125</v>
+        <v>627.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Australia</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>292.15</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>128.546</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>116.86</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>46.744</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>584.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Middle East &amp; Africa</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>189.5394</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>124.3681</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>83.36790000000001</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>243.1122</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>640.3876</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tunisia</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>73.7839</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>44.2703</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>29.5136</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>98.3785</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>245.9463</v>
+      <c r="B20" s="7" t="n">
+        <v>408.3346</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>163.3338</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>304.0916</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>531.8182</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1407.5782</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Morocco</t>
+          <t xml:space="preserve">   Tunisia</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>41.0228</v>
+        <v>69.69459999999999</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>25.9811</v>
+        <v>27.8778</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>17.7765</v>
+        <v>55.7556</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>51.9621</v>
+        <v>125.4502</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>136.7425</v>
+        <v>278.7782</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Algeria</t>
+          <t xml:space="preserve">   Morocco</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>74.73269999999999</v>
+        <v>338.64</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>54.1167</v>
+        <v>135.456</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>36.0778</v>
+        <v>248.336</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>92.77160000000001</v>
+        <v>406.368</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>257.6988</v>
+        <v>1128.8</v>
       </c>
     </row>
     <row r="23">
@@ -4481,41 +2821,41 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>7.9136</v>
+        <v>2592.675</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>6.2179</v>
+        <v>1037.07</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3.9568</v>
+        <v>1267.53</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10.1747</v>
+        <v>864.225</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Syria</t>
+          <t xml:space="preserve">   Rest of World</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>7.9136</v>
+        <v>2592.675</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>6.2179</v>
+        <v>1037.07</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>3.9568</v>
+        <v>1267.53</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>10.1747</v>
+        <v>864.225</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>28.263</v>
+        <v>5761.5</v>
       </c>
     </row>
     <row r="26">
@@ -4533,29 +2873,29 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Glass Bottles and Jars</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Plastic Bottles and Containers</t>
+          <t>Foodservice</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Metal Cans and Tins</t>
+          <t>Food Processing</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Bulk (Drums, IBCs, Flexitanks)</t>
+          <t>Bulk/Industrial</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
@@ -4565,29 +2905,859 @@
         <v>0.18</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>By Packaging Format -- TOP-DOWN (country total x share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Evidence status: web_evidence_backed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Bottles (Glass/Plastic)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Cans/Tins</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Bulk Containers (Drums, IBCs, Flexitanks)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>13336.1753</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>4496.7273</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1142.0887</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>4680.3445</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>23655.3358</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>2339.54</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>756.91</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>137.62</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>206.43</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>3440.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   United States</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2339.54</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>756.91</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>137.62</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>206.43</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>3440.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>538.17</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>197.329</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>44.8475</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>116.6035</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>896.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Brazil</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>538.17</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>197.329</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>44.8475</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>116.6035</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>896.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>5896.814</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1949.2776</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>546.8603000000001</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>2544.2557</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>10937.2076</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Italy</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>2106.6725</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>617.473</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>181.6097</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>726.4387</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>3632.1939</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Spain</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>1631.3827</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>577.7814</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>169.9357</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1019.6141</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>3398.7139</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Greece</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>340.5822</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>111.4633</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>30.962</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>136.2328</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>619.2403</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Portugal</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>386.152</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>133.668</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>185.65</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>742.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Turkey</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>664.25</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>265.7</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>66.425</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>332.125</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>1328.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   France</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>467.0478</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>150.6606</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>37.6651</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>97.9294</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>753.3029</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Germany</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>300.7268</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>92.5313</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>23.1328</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>46.2657</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>462.6566</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Asia Pacific</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>807.2190000000001</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>229.774</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>54.307</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1211.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Japan</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>439.11</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>112.914</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>25.092</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>50.184</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>627.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Australia</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>368.109</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>116.86</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>29.215</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>70.116</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>584.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Middle East &amp; Africa</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>585.6073</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>211.1367</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>70.3789</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>540.4553</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1407.5782</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tunisia</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>111.5113</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>41.8167</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>13.9389</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>111.5113</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>278.7782</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Morocco</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>474.096</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>428.944</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>1128.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>3168.825</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1152.3</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>288.075</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>1152.3</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>5761.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Rest of World</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>3168.825</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1152.3</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>288.075</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>1152.3</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>5761.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Shares used (fraction of each country's total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Bottles (Glass/Plastic)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Cans/Tins</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Bulk Containers (Drums, IBCs, Flexitanks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Italy</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
         <v>0.48</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
@@ -4597,54 +3767,54 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>0.44</v>
+        <v>0.68</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>0.18</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
@@ -4654,168 +3824,766 @@
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="C33" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>0.28</v>
+        <v>0.42</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>By Source/Origin -- TOP-DOWN (country total x share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Evidence status: web_evidence_backed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Conventional</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Organic</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>20417.1282</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3238.2076</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>23655.3358</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>3027.64</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>412.86</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>3440.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   United States</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>3027.64</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>412.86</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>3440.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>771.377</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>125.573</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>896.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Brazil</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>771.377</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>125.573</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>896.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>9156.5558</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1780.6518</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>10937.2076</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Italy</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>2978.399</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>653.7949</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>3632.1939</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Spain</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>2888.9068</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>509.8071</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>3398.7139</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Greece</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>495.3922</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>123.8481</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>619.2403</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Portugal</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>623.784</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>118.816</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>742.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Turkey</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1235.505</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>92.995</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1328.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   France</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>587.5762999999999</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>165.7266</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>753.3029</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Germany</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>346.9925</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>115.6641</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>462.6566</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Asia Pacific</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>986.809</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>224.791</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1211.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Japan</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>501.84</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>125.46</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>627.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Australia</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>484.969</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>99.331</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>584.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Middle East &amp; Africa</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>1289.3964</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>118.1818</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1407.5782</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tunisia</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>250.9004</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>27.8778</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>278.7782</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Morocco</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>1038.496</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>90.304</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>1128.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>5185.35</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>576.15</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>5761.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Rest of World</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>5185.35</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>576.15</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>5761.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Shares used (fraction of each country's total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Conventional</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Organic</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Japan</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
       <c r="B41" s="10" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -4933,19 +4701,19 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>The extra virgin olive oil segment represents the dominant force in the olive oil market, capturing approximately 58.0% of total market share in 2025. | Within the olive oil market, Extra Virgin Olive Oil is the leading product segment, accounting for approximately 45% of global market share in 2025. | Virgin olive oils are projected to account for 78.65% of the global market in 2026.</t>
+          <t>The extra virgin olive oil segment accounted for a share of 45% in 2025 | refined oil held 43.28% of the olive oil market share in 2025 | Extra virgin olive oil at 18.4% commands the premium segment</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>The shares are estimated based on web snippets and industry knowledge. The snippets indicate that extra virgin olive oil is the dominant segment globally, with shares ranging from 45% to 58%. Virgin olive oil is also significant, with a combined virgin olive oil share (including extra virgin) of 78.65% in 2026. Refined and pomace oils make up the remainder. Country-level shares are adjusted based on typical consumption patterns: Greece has the highest extra virgin share due to its traditional production and consumption; Spain has a significant refined oil segment due to its large-scale production and export of refined oils; Italy has a strong extra virgin focus but also a notable refined segment; non-Mediterranean countries like the US, Brazil, and Japan have higher extra virgin shares due to premiumization trends. The evidence quotes are verbatim from the snippets.</t>
+          <t>The global olive oil market is valued at approximately $22 billion in 2025. The product grade segmentation is not uniformly reported across sources; some provide conflicting figures (e.g., extra virgin at 45% vs. 18.4%, refined at 43.28%, virgin at 40%). These discrepancies likely arise from different definitions (e.g., whether 'virgin' includes extra virgin) and varying market scopes. Based on industry knowledge and the snippets, extra virgin olive oil is the dominant grade in most producing and consuming countries, with shares ranging from 45% to 75%. Virgin olive oil typically holds 15-20%, refined olive oil 8-30%, and blended/refined NES 5-10%. Country-level shares are estimated using typical consumption patterns: Greece has the highest extra virgin share due to traditional production and consumption; Spain has a more balanced mix due to large-scale refining and blending for export; Italy has a high extra virgin share due to premium positioning; non-Mediterranean countries like the US, Germany, and Brazil have lower extra virgin shares due to price sensitivity and higher use of refined/blended oils. The 'Rest of World' category has a lower extra virgin share as it includes many emerging markets where refined and blended oils are more common.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>By Extraction Method</t>
+          <t>By Distribution Channel</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -4965,19 +4733,19 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Global Olive Oil Market to 2032, By Extraction Method Cold-Extracted is the largest segment in Global Olive Oil Market to 2032 with a revenue of 6,311.17 USD Billion in the year 2024. | The extra virgin olive oil segment accounted for a share of 45% in 2025, owing to strong consumer preference for naturally extracted and minimally processed oils associated with high quality, authentic flavor, and nutritional value. | It means the oil was extracted using only mechanical methods, at temperatures below 27°C (80.6°F), with no chemicals and no refining.</t>
+          <t>Retail/household end-users are expected to hold 63.71% of the market share in 2026. | Supermarkets and hypermarkets lead the distribution channel segment at 56.8%, supported by olive oil's grocery staple status. | Household/retail segment held the largest market share in 2023. | Based on application, the food &amp; beverage segment accounted for the largest market share of 69.10% in 2025.</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>The snippets give no country-level split by extraction method, so country shares are estimated from industry knowledge of production/consumption structures. Cold-pressed/cold-extracted (essentially EVOO and virgin grades) dominates globally, consistent with the snippet calling cold-extracted the largest segment and EVOO at 45% of product-type value. Traditional producing countries (Spain, Italy, Greece, Portugal) have high cold-pressed shares because most premium and export volume is virgin/EVOO, but they also process significant volumes of lower-grade/hot-pressed and pomace/refined oil, so chemical/refining shares are modest (6-10%). Greece has the highest virgin/EVOO orientation. North African and Middle Eastern producers (Tunisia, Turkey, Morocco, Syria, Algeria) have more bulk/commodity and refined/pomace output, so cold-pressed shares are lower and hot-pressed plus chemical/refining shares higher. Import-dependent consumer markets (US, France, Germany, Brazil, Japan) skew toward bottled EVOO/virgin for retail, giving higher cold-pressed shares, with Germany/Japan/Brazil having somewhat larger refined/pomace shares via private label and foodservice. All figures are analyst estimates, not sourced country data.</t>
+          <t>No snippet gives a country-by-country split across the four distribution-channel segments, so these are analyst estimates grounded in olive-oil trade structure and the few figures available. The snippets support a globally retail-dominant pattern (household/retail ~63.7% of end-users; supermarkets/hypermarkets 56.8% of distribution; food &amp; beverage applications 69.1%), which I applied most strongly to high-income importing countries (US, Germany, France, Japan, Australia) where packaged retail and foodservice dominate and little bulk/industrial olive oil is used. Producer/exporting countries (Spain, Tunisia, Morocco, Turkey, Portugal, Italy) shift substantial volume into bulk/industrial and food-processing channels because they export in bulk and supply canning, baking, and ingredient industries; Tunisia and Morocco are the most bulk-oriented given their large bulk export trade, while Greece skews most to retail/foodservice due to high domestic per-capita consumption. Italy and Spain retain large food-processing shares from domestic food manufacturing and branded bottling. These are best-estimate fractions summing to 1 per country, not sourced country-level data.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>By Distribution Channel</t>
+          <t>By Packaging Format</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -4997,19 +4765,19 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Edible Olive Oil Market By Distribution Channel (USD Billion, 2019-2035). Online Retail. Supermarkets/Hypermarkets.</t>
+          <t>The report “Olive Oil Market Share, Size, Trends, Industry Analysis Report, By Packaging (Pouches, Cans, Bottles); By Type; By Application; By Distribution Channel; By Region; Segment Forecast, 2026 - 2034” gives a detailed insight into current ... | U.S. Olive Oil Market (2025 - 2030) Size, Share &amp; Trends Analysis Report By Type (Refined, Virgin, Extra Virgin), By Packaging (Bottle, Pouches, Cans), By Application (Food &amp; Beverage, Personal Care And Cosmetics), By Distribution Channel, And Segment Forecasts</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>The snippets confirm the standard segmentation (supermarkets/hypermarkets, online, specialty stores, others) but provide no country-level figures, so all shares are estimated from industry knowledge. In producing/consuming Mediterranean countries (Spain, Italy, Greece, Portugal, Tunisia, Turkey, Morocco, Syria, Algeria), supermarkets dominate but direct-from-producer/bulk sales and foodservice carry meaningful shares because of local milling, bulk buying, and restaurant use; Syria, Morocco, and Algeria skew most heavily to direct/bulk. In import-dependent markets (US, France, Germany, Brazil, Japan), supermarkets/hypermarkets take the largest share, with specialty/gourmet and online retail stronger in the US, Japan, and Germany, and foodservice notable in France and Brazil. Online retail is generally smallest in North Africa and the Middle East due to lower e-commerce penetration.</t>
+          <t>The snippets confirm that packaging is a standard segmentation dimension (bottles, cans, pouches) but provide no country-level value splits by packaging format. Shares are therefore estimated using industry knowledge: consumer markets (US, Japan, Germany, France, Australia, Brazil) skew heavily toward retail bottles; producing/exporting countries (Spain, Tunisia, Morocco, Portugal, Turkey, Greece, Italy) have larger bulk container shares due to export trade in drums, IBCs and flexitanks; cans/tins are a modest but growing format everywhere; jars remain a small niche. Fractions are set to sum to 1 per country.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>By Packaging Format</t>
+          <t>By Source/Origin</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -5029,12 +4797,12 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>By packaging: Bottle segment accounted for the largest share of 53.6% in 2025.</t>
+          <t>Virgin olive oil dominates the type segment with a 61.9% share in 2025, reflecting established household culinary use and broad price-point accessibility across mass-market retail. | Extra virgin olive oil at 18.4% commands the premium segment, growing at approximately 4.6% CAGR driven by health-conscious demand.</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>The snippets give only one directly usable figure: a global 'Bottle segment' share of 53.6% in 2025, which I treat as an anchor for glass bottles in consumer-oriented markets. No snippet provides country-level packaging splits, so country shares are estimated from industry knowledge. Producer/export-heavy countries (Spain, Italy, Greece, Portugal, Tunisia, Turkey, Morocco, Syria, Algeria) have larger bulk shares because much volume moves in drums, IBCs and flexitanks for export and industrial use; Spain and Tunisia tilt most to bulk. Importing consumer markets (US, France, Germany, Japan, Brazil) skew to glass bottles for premium retail, with the US highest on glass and lowest on bulk. Plastic bottles/containers take a mid-teens to low-20s share, larger in price-sensitive emerging markets; metal cans/tins are a small niche (foodservice, flavored, gift). Shares are my estimates, not sourced country data.</t>
+          <t>The web snippets provide no direct figures on the conventional vs. organic split by country, so these are best-estimate industry figures. Organic olive oil typically represents roughly 10-25% of value in mature, high-income markets (Germany, France, Italy, Greece, Japan) and lower shares (5-15%) in lower-income or production-focused markets (Turkey, Tunisia, Morocco, Rest of World). Conventional dominates everywhere due to price accessibility and mass-market retail presence, consistent with the snippet noting virgin olive oil's 61.9% share and broad price-point accessibility.</t>
         </is>
       </c>
     </row>
@@ -5106,7 +4874,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>By Extraction Method</t>
+          <t>By Distribution Channel</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5124,7 +4892,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>By Distribution Channel</t>
+          <t>By Packaging Format</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5142,7 +4910,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>By Packaging Format</t>
+          <t>By Source/Origin</t>
         </is>
       </c>
       <c r="B17" t="n">
